--- a/erp-server/erp-server-file/src/main/resources/excel/wms/fbaDelivery.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/fbaDelivery.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>单据编号</t>
   </si>
@@ -37,6 +37,12 @@
     <t>来源单号</t>
   </si>
   <si>
+    <t>海外仓入库单号</t>
+  </si>
+  <si>
+    <t>FBA货件号</t>
+  </si>
+  <si>
     <t>物流单状态</t>
   </si>
   <si>
@@ -46,6 +52,9 @@
     <t>备货类型</t>
   </si>
   <si>
+    <t>装箱状态</t>
+  </si>
+  <si>
     <t>审核状态</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>发货数量</t>
   </si>
   <si>
+    <t>装箱数量</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -118,6 +130,12 @@
     <t>{.sourceCode}</t>
   </si>
   <si>
+    <t>{.overseasInboundCode}</t>
+  </si>
+  <si>
+    <t>{.fbaShipmentCode}</t>
+  </si>
+  <si>
     <t>{.logisticsStatusName}</t>
   </si>
   <si>
@@ -127,6 +145,9 @@
     <t>{.demandTypeName}</t>
   </si>
   <si>
+    <t>{.packingStatusName}</t>
+  </si>
+  <si>
     <t>{.approveStatusName}</t>
   </si>
   <si>
@@ -173,6 +194,9 @@
   </si>
   <si>
     <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.packingQty}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1186,51 +1210,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="8.5" customWidth="1"/>
-    <col min="6" max="6" width="8.125" customWidth="1"/>
-    <col min="7" max="7" width="8.75" customWidth="1"/>
-    <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="24.625" customWidth="1"/>
-    <col min="12" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="15" width="9.25" customWidth="1"/>
-    <col min="16" max="16" width="9.75" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="36.375" customWidth="1"/>
-    <col min="19" max="19" width="10.375" customWidth="1"/>
-    <col min="21" max="21" width="8.875" customWidth="1"/>
-    <col min="22" max="22" width="31.25" customWidth="1"/>
-    <col min="24" max="24" width="17.375" customWidth="1"/>
-    <col min="26" max="26" width="9.375" customWidth="1"/>
-    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="8" width="8.5" customWidth="1"/>
+    <col min="9" max="9" width="8.125" customWidth="1"/>
+    <col min="10" max="10" width="8.75" customWidth="1"/>
+    <col min="11" max="11" width="21.75" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="24.625" customWidth="1"/>
+    <col min="15" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="9.5" customWidth="1"/>
+    <col min="18" max="18" width="9.25" customWidth="1"/>
+    <col min="19" max="19" width="9.75" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="21" max="21" width="36.375" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="24" max="25" width="8.875" customWidth="1"/>
+    <col min="26" max="26" width="31.25" customWidth="1"/>
+    <col min="28" max="28" width="17.375" customWidth="1"/>
+    <col min="30" max="30" width="9.375" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1296,88 +1320,112 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:31">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/fbaDelivery.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/fbaDelivery.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>单据编号</t>
   </si>
@@ -58,6 +58,9 @@
     <t>审核状态</t>
   </si>
   <si>
+    <t>中转仓</t>
+  </si>
+  <si>
     <t>作废状态</t>
   </si>
   <si>
@@ -149,6 +152,9 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.transferWarehouseNames}</t>
   </si>
   <si>
     <t>{.invalidStatusName}</t>
@@ -852,7 +858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -860,6 +866,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -1218,27 +1227,28 @@
     <col min="5" max="5" width="12.375" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="8" width="8.5" customWidth="1"/>
-    <col min="9" max="9" width="8.125" customWidth="1"/>
-    <col min="10" max="10" width="8.75" customWidth="1"/>
-    <col min="11" max="11" width="21.75" customWidth="1"/>
-    <col min="12" max="12" width="6" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="24.625" customWidth="1"/>
-    <col min="15" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="9.5" customWidth="1"/>
-    <col min="18" max="18" width="9.25" customWidth="1"/>
-    <col min="19" max="19" width="9.75" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="36.375" customWidth="1"/>
-    <col min="22" max="22" width="10.375" customWidth="1"/>
-    <col min="24" max="25" width="8.875" customWidth="1"/>
-    <col min="26" max="26" width="31.25" customWidth="1"/>
-    <col min="28" max="28" width="17.375" customWidth="1"/>
-    <col min="30" max="30" width="9.375" customWidth="1"/>
-    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="20.75" customWidth="1"/>
+    <col min="11" max="11" width="8.75" customWidth="1"/>
+    <col min="12" max="12" width="21.75" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="24.625" customWidth="1"/>
+    <col min="16" max="17" width="13.5" customWidth="1"/>
+    <col min="18" max="18" width="9.5" customWidth="1"/>
+    <col min="19" max="19" width="9.25" customWidth="1"/>
+    <col min="20" max="20" width="9.75" customWidth="1"/>
+    <col min="21" max="21" width="9" customWidth="1"/>
+    <col min="22" max="22" width="36.375" customWidth="1"/>
+    <col min="23" max="23" width="10.375" customWidth="1"/>
+    <col min="25" max="26" width="8.875" customWidth="1"/>
+    <col min="27" max="27" width="31.25" customWidth="1"/>
+    <col min="29" max="29" width="17.375" customWidth="1"/>
+    <col min="31" max="31" width="9.375" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1276,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1332,100 +1342,106 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="J2" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="M2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="O2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S2" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="T2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="W2" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="X2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB2" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="AB2" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="AC2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
